--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:57</t>
+    <t xml:space="preserve">2026-09-09 19:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:23</t>
+    <t xml:space="preserve">2026-09-17 03:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:54</t>
+    <t xml:space="preserve">2026-09-27 02:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:17</t>
+    <t xml:space="preserve">2026-10-02 23:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:35</t>
+    <t xml:space="preserve">2026-10-05 05:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Valparaiso</t>
+    <t xml:space="preserve">Region de Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t xml:space="preserve">Indice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Isla de Pascua</t>
@@ -728,7 +725,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>153.25</v>
@@ -736,7 +733,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>62.69</v>
@@ -744,7 +741,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>119.41</v>
@@ -752,7 +749,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>140.22</v>
@@ -760,7 +757,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>122.91</v>
@@ -768,7 +765,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>150.31</v>
@@ -776,7 +773,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>112.71</v>
@@ -784,7 +781,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>143.36</v>
